--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122881941</v>
       </c>
       <c r="B2" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122881941</v>
       </c>
       <c r="B2" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122881941</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122881941</v>
       </c>
       <c r="B2" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122881941</v>
       </c>
       <c r="B2" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122881941</v>
+        <v>86753584</v>
       </c>
       <c r="B2" t="n">
-        <v>100645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gäddeholm, Vstm</t>
+          <t>Rosendal, VNV om, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596039</v>
+        <v>596121</v>
       </c>
       <c r="R2" t="n">
-        <v>6602299</v>
+        <v>6602300</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stort antal</t>
+          <t>Östra vägkanten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,18 +773,451 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122881922</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gäddeholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>596031</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6602324</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kärrbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Molly Wikingson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Molly Wikingson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122881930</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>596038, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596038</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6602321</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kärrbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122881941</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gäddeholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596039</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6602299</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kärrbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stort antal</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122881961</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gäddeholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595990</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6602298</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kärrbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flertal</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30759-2022 artfynd.xlsx
+++ b/artfynd/A 30759-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122881922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122881961</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86753584</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122881930</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,8 +1243,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122881941</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>